--- a/output/pdf_financials_xlsx/GST.xlsx
+++ b/output/pdf_financials_xlsx/GST.xlsx
@@ -5358,43 +5358,43 @@
         <v>0.917441</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.13457</v>
+        <v>1.20836</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.297619</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.355446</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.400184</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.448015</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.555108</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.68027</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.723965</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.696739</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.696739</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.696739</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.696739</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.696739</v>
       </c>
     </row>
     <row r="93">
@@ -8302,7 +8302,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -9538,7 +9542,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10540,7 +10548,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -10790,7 +10802,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GST.xlsx
+++ b/output/pdf_financials_xlsx/GST.xlsx
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-9e-06</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00051</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000158</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000204</v>
       </c>
     </row>
     <row r="13">
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.07535699999999999</v>
+        <v>-0.07530199999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.059218</v>
+        <v>-0.059209</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.052324</v>
+        <v>-0.051814</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.185226</v>
+        <v>-0.185068</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.12295</v>
+        <v>-0.122746</v>
       </c>
     </row>
     <row r="28">
@@ -2101,19 +2101,19 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.07535699999999999</v>
+        <v>-0.07530199999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.059218</v>
+        <v>-0.059209</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.052324</v>
+        <v>-0.051814</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.185226</v>
+        <v>-0.185068</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.12295</v>
+        <v>-0.122746</v>
       </c>
     </row>
     <row r="30">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
